--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD_FMRAD/rwd-only/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -468,26 +468,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.06</t>
+          <t>0.64 ± 0.05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.56 ± 0.09</t>
+          <t>0.57 ± 0.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.62 ± 0.15</t>
+          <t>0.69 ± 0.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.57 ± 0.25</t>
+          <t>0.49 ± 0.13</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>353</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3">
@@ -498,26 +498,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.69 ± 0.13</t>
+          <t>0.75 ± 0.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4">
@@ -528,26 +528,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.58 ± 0.17</t>
+          <t>0.51 ± 0.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/mlef_pipeline/results/DCR/IO_ONLY/RWD_FMRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/DCR/IO_ONLY/RWD_FMRAD/rwd-only/results.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.69 ± 0.12</t>
+          <t>0.70 ± 0.11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -528,12 +528,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.51 ± 0.16</t>
+          <t>0.52 ± 0.16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F4" t="n">
